--- a/test_sheetMaker.xlsx
+++ b/test_sheetMaker.xlsx
@@ -413,9 +413,255 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="B2:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Water/Aqua/Eau</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Cocamidopropyl Hydroxysultaine</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sodium Cocoyl Glutamate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sorbeth-230 Tetraoleate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Polysorbate 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sodium Chloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aloe Barbadensis Leaf (Aloe Vera) Juice Powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Brassica Oleracea Acephala (Kale) Leaf Extract</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Spinacia Oleracea (Spinach) Leaf Extract</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Camellia Sinensis (Green Tea) Leaf Extract</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Medicago Sativa (Alfalfa) Extract</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chamomilla Recutita (Matricaria) Flower Extract</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tetrahexyldecyl Ascorbate (Vitamin C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Glycerin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Panthenol (Vitamin B5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tocopheryl Acetate (Vitamin E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Decyl Glucoside</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sorbitan Laurate</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tetrasodium Glutamate Diacetate</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gluconolactone</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ethylhexylglycerin</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Maltodextrin</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Citric Acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Phenoxyethanol</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Potassium Sorbate</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sodium Benzoate</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gardenia Jasminoides (Jasmine) Fruit Extract</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fragrance/Parfum</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sodium Hydroxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sodium Glycolate</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sodium Formate</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Hexyl Cinnamal</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Linalool</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Limonene</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Chlorophyllin-Copper Complex (CI 75810)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>